--- a/Employee_Reports_wi48/Ivan Raphael Macatangay Del Mundo Q0543.xlsx
+++ b/Employee_Reports_wi48/Ivan Raphael Macatangay Del Mundo Q0543.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1509,11 +1509,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-113</v>
+        <v>-116</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-114</v>
+        <v>-117</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1815,9 +1815,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
           <t>05-Apr-2025</t>
@@ -1829,11 +1841,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-99</v>
+        <v>-102</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1878,11 +1890,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1927,11 +1939,11 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1976,11 +1988,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2025,11 +2037,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -2062,11 +2074,11 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2099,11 +2111,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -2148,11 +2160,11 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2197,11 +2209,11 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2246,11 +2258,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-55</v>
+        <v>-58</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2295,11 +2307,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2344,11 +2356,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2393,11 +2405,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2442,11 +2454,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2479,11 +2491,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2516,11 +2528,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2553,11 +2565,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2590,11 +2602,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -3133,7 +3145,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3228,7 +3240,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7981</v>
+        <v>7978</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3257,7 +3269,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7977</v>
+        <v>7974</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3286,7 +3298,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7976</v>
+        <v>7973</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3315,7 +3327,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7983</v>
+        <v>7980</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
